--- a/test_items.xlsx
+++ b/test_items.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Web" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="導入・アクセス方法" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="凡例" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="フロントページ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49,7 +50,7 @@
     </font>
     <font/>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -101,8 +102,13 @@
         <fgColor rgb="00F3EEF8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006A0572"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -116,11 +122,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -152,6 +186,14 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -584,14 +626,14 @@
           <t>■ help</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
+      <c r="B2" s="13" t="n"/>
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="13" t="n"/>
+      <c r="G2" s="13" t="n"/>
+      <c r="H2" s="13" t="n"/>
+      <c r="I2" s="14" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -673,14 +715,14 @@
           <t>■ ip</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -910,14 +952,14 @@
           <t>■ start/stop</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
+      <c r="B12" s="13" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="13" t="n"/>
+      <c r="I12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1147,14 +1189,14 @@
           <t>■ exit</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="14" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1273,14 +1315,14 @@
           <t>■ backup</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="13" t="n"/>
+      <c r="I23" s="14" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1695,14 +1737,14 @@
           <t>■ cmd</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="n"/>
+      <c r="B35" s="13" t="n"/>
+      <c r="C35" s="13" t="n"/>
+      <c r="D35" s="13" t="n"/>
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="13" t="n"/>
+      <c r="G35" s="13" t="n"/>
+      <c r="H35" s="13" t="n"/>
+      <c r="I35" s="14" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -1932,14 +1974,14 @@
           <t>■ cmd stdin</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n"/>
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="n"/>
-      <c r="G42" s="3" t="n"/>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
+      <c r="B42" s="13" t="n"/>
+      <c r="C42" s="13" t="n"/>
+      <c r="D42" s="13" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
+      <c r="G42" s="13" t="n"/>
+      <c r="H42" s="13" t="n"/>
+      <c r="I42" s="14" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -4167,14 +4209,14 @@
           <t>■ logs</t>
         </is>
       </c>
-      <c r="B103" s="3" t="n"/>
-      <c r="C103" s="3" t="n"/>
-      <c r="D103" s="3" t="n"/>
-      <c r="E103" s="3" t="n"/>
-      <c r="F103" s="3" t="n"/>
-      <c r="G103" s="3" t="n"/>
-      <c r="H103" s="3" t="n"/>
-      <c r="I103" s="3" t="n"/>
+      <c r="B103" s="13" t="n"/>
+      <c r="C103" s="13" t="n"/>
+      <c r="D103" s="13" t="n"/>
+      <c r="E103" s="13" t="n"/>
+      <c r="F103" s="13" t="n"/>
+      <c r="G103" s="13" t="n"/>
+      <c r="H103" s="13" t="n"/>
+      <c r="I103" s="14" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
@@ -4330,14 +4372,14 @@
           <t>■ lang</t>
         </is>
       </c>
-      <c r="B108" s="3" t="n"/>
-      <c r="C108" s="3" t="n"/>
-      <c r="D108" s="3" t="n"/>
-      <c r="E108" s="3" t="n"/>
-      <c r="F108" s="3" t="n"/>
-      <c r="G108" s="3" t="n"/>
-      <c r="H108" s="3" t="n"/>
-      <c r="I108" s="3" t="n"/>
+      <c r="B108" s="13" t="n"/>
+      <c r="C108" s="13" t="n"/>
+      <c r="D108" s="13" t="n"/>
+      <c r="E108" s="13" t="n"/>
+      <c r="F108" s="13" t="n"/>
+      <c r="G108" s="13" t="n"/>
+      <c r="H108" s="13" t="n"/>
+      <c r="I108" s="14" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -4456,14 +4498,14 @@
           <t>■ permission</t>
         </is>
       </c>
-      <c r="B112" s="3" t="n"/>
-      <c r="C112" s="3" t="n"/>
-      <c r="D112" s="3" t="n"/>
-      <c r="E112" s="3" t="n"/>
-      <c r="F112" s="3" t="n"/>
-      <c r="G112" s="3" t="n"/>
-      <c r="H112" s="3" t="n"/>
-      <c r="I112" s="3" t="n"/>
+      <c r="B112" s="13" t="n"/>
+      <c r="C112" s="13" t="n"/>
+      <c r="D112" s="13" t="n"/>
+      <c r="E112" s="13" t="n"/>
+      <c r="F112" s="13" t="n"/>
+      <c r="G112" s="13" t="n"/>
+      <c r="H112" s="13" t="n"/>
+      <c r="I112" s="14" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
@@ -4656,14 +4698,14 @@
           <t>■ tokengen</t>
         </is>
       </c>
-      <c r="B118" s="3" t="n"/>
-      <c r="C118" s="3" t="n"/>
-      <c r="D118" s="3" t="n"/>
-      <c r="E118" s="3" t="n"/>
-      <c r="F118" s="3" t="n"/>
-      <c r="G118" s="3" t="n"/>
-      <c r="H118" s="3" t="n"/>
-      <c r="I118" s="3" t="n"/>
+      <c r="B118" s="13" t="n"/>
+      <c r="C118" s="13" t="n"/>
+      <c r="D118" s="13" t="n"/>
+      <c r="E118" s="13" t="n"/>
+      <c r="F118" s="13" t="n"/>
+      <c r="G118" s="13" t="n"/>
+      <c r="H118" s="13" t="n"/>
+      <c r="I118" s="14" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="n">
@@ -4745,14 +4787,14 @@
           <t>■ update</t>
         </is>
       </c>
-      <c r="B121" s="3" t="n"/>
-      <c r="C121" s="3" t="n"/>
-      <c r="D121" s="3" t="n"/>
-      <c r="E121" s="3" t="n"/>
-      <c r="F121" s="3" t="n"/>
-      <c r="G121" s="3" t="n"/>
-      <c r="H121" s="3" t="n"/>
-      <c r="I121" s="3" t="n"/>
+      <c r="B121" s="13" t="n"/>
+      <c r="C121" s="13" t="n"/>
+      <c r="D121" s="13" t="n"/>
+      <c r="E121" s="13" t="n"/>
+      <c r="F121" s="13" t="n"/>
+      <c r="G121" s="13" t="n"/>
+      <c r="H121" s="13" t="n"/>
+      <c r="I121" s="14" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="n">
@@ -4945,14 +4987,14 @@
           <t>■ announce</t>
         </is>
       </c>
-      <c r="B127" s="3" t="n"/>
-      <c r="C127" s="3" t="n"/>
-      <c r="D127" s="3" t="n"/>
-      <c r="E127" s="3" t="n"/>
-      <c r="F127" s="3" t="n"/>
-      <c r="G127" s="3" t="n"/>
-      <c r="H127" s="3" t="n"/>
-      <c r="I127" s="3" t="n"/>
+      <c r="B127" s="13" t="n"/>
+      <c r="C127" s="13" t="n"/>
+      <c r="D127" s="13" t="n"/>
+      <c r="E127" s="13" t="n"/>
+      <c r="F127" s="13" t="n"/>
+      <c r="G127" s="13" t="n"/>
+      <c r="H127" s="13" t="n"/>
+      <c r="I127" s="14" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="n">
@@ -5219,14 +5261,14 @@
           <t>■ terminal</t>
         </is>
       </c>
-      <c r="B135" s="3" t="n"/>
-      <c r="C135" s="3" t="n"/>
-      <c r="D135" s="3" t="n"/>
-      <c r="E135" s="3" t="n"/>
-      <c r="F135" s="3" t="n"/>
-      <c r="G135" s="3" t="n"/>
-      <c r="H135" s="3" t="n"/>
-      <c r="I135" s="3" t="n"/>
+      <c r="B135" s="13" t="n"/>
+      <c r="C135" s="13" t="n"/>
+      <c r="D135" s="13" t="n"/>
+      <c r="E135" s="13" t="n"/>
+      <c r="F135" s="13" t="n"/>
+      <c r="G135" s="13" t="n"/>
+      <c r="H135" s="13" t="n"/>
+      <c r="I135" s="14" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="n">
@@ -5419,14 +5461,14 @@
           <t>■ status</t>
         </is>
       </c>
-      <c r="B141" s="3" t="n"/>
-      <c r="C141" s="3" t="n"/>
-      <c r="D141" s="3" t="n"/>
-      <c r="E141" s="3" t="n"/>
-      <c r="F141" s="3" t="n"/>
-      <c r="G141" s="3" t="n"/>
-      <c r="H141" s="3" t="n"/>
-      <c r="I141" s="3" t="n"/>
+      <c r="B141" s="13" t="n"/>
+      <c r="C141" s="13" t="n"/>
+      <c r="D141" s="13" t="n"/>
+      <c r="E141" s="13" t="n"/>
+      <c r="F141" s="13" t="n"/>
+      <c r="G141" s="13" t="n"/>
+      <c r="H141" s="13" t="n"/>
+      <c r="I141" s="14" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="4" t="n">
@@ -5597,14 +5639,14 @@
           <t>■ 認証</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
+      <c r="B2" s="13" t="n"/>
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="13" t="n"/>
+      <c r="G2" s="13" t="n"/>
+      <c r="H2" s="13" t="n"/>
+      <c r="I2" s="14" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -5760,14 +5802,14 @@
           <t>■ ダッシュボード</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
+      <c r="B7" s="13" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
+      <c r="H7" s="13" t="n"/>
+      <c r="I7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -6071,14 +6113,14 @@
           <t>■ サーバー制御</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="13" t="n"/>
+      <c r="I16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -6308,14 +6350,14 @@
           <t>■ バックアップ</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
+      <c r="G23" s="13" t="n"/>
+      <c r="H23" s="13" t="n"/>
+      <c r="I23" s="14" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -6804,14 +6846,14 @@
           <t>■ ファイル管理</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="n"/>
-      <c r="H37" s="3" t="n"/>
-      <c r="I37" s="3" t="n"/>
+      <c r="B37" s="13" t="n"/>
+      <c r="C37" s="13" t="n"/>
+      <c r="D37" s="13" t="n"/>
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="13" t="n"/>
+      <c r="G37" s="13" t="n"/>
+      <c r="H37" s="13" t="n"/>
+      <c r="I37" s="14" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -8410,14 +8452,14 @@
           <t>■ ログ</t>
         </is>
       </c>
-      <c r="B81" s="3" t="n"/>
-      <c r="C81" s="3" t="n"/>
-      <c r="D81" s="3" t="n"/>
-      <c r="E81" s="3" t="n"/>
-      <c r="F81" s="3" t="n"/>
-      <c r="G81" s="3" t="n"/>
-      <c r="H81" s="3" t="n"/>
-      <c r="I81" s="3" t="n"/>
+      <c r="B81" s="13" t="n"/>
+      <c r="C81" s="13" t="n"/>
+      <c r="D81" s="13" t="n"/>
+      <c r="E81" s="13" t="n"/>
+      <c r="F81" s="13" t="n"/>
+      <c r="G81" s="13" t="n"/>
+      <c r="H81" s="13" t="n"/>
+      <c r="I81" s="14" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -8684,14 +8726,14 @@
           <t>■ ステータス</t>
         </is>
       </c>
-      <c r="B89" s="3" t="n"/>
-      <c r="C89" s="3" t="n"/>
-      <c r="D89" s="3" t="n"/>
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" s="3" t="n"/>
-      <c r="G89" s="3" t="n"/>
-      <c r="H89" s="3" t="n"/>
-      <c r="I89" s="3" t="n"/>
+      <c r="B89" s="13" t="n"/>
+      <c r="C89" s="13" t="n"/>
+      <c r="D89" s="13" t="n"/>
+      <c r="E89" s="13" t="n"/>
+      <c r="F89" s="13" t="n"/>
+      <c r="G89" s="13" t="n"/>
+      <c r="H89" s="13" t="n"/>
+      <c r="I89" s="14" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -8972,9 +9014,9 @@
           <t>【導入手順】</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
+      <c r="B2" s="13" t="n"/>
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="14" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -9132,9 +9174,9 @@
           <t>【Discord bot アクセス方法】</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -9204,9 +9246,9 @@
           <t>【Web 管理画面 アクセス方法】</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
@@ -9316,9 +9358,9 @@
           <t>【Java 版サーバー向け補足】</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="13" t="n"/>
+      <c r="D38" s="14" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -9472,4 +9514,3515 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I99"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>ページ</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>機能・操作</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>事前条件</t>
+        </is>
+      </c>
+      <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>結果</t>
+        </is>
+      </c>
+      <c r="I1" s="15" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>■ ログイン</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>ログイン</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>トークン入力・ログイン</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>有効なトークンが発行済み（/tokengen 実行済み）</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>ログインページでトークンを入力して Login ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>ダッシュボードページに遷移する</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>ログイン</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>トークン入力・ログイン</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>無効 / 期限切れトークンを使用</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>ログインページで誤ったトークンを入力して Login ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>ページが再表示され赤いエラーメッセージ（'Invalid token...'）が表示される</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>ログイン</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>トークン入力・ログイン</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>未入力状態</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>トークン欄を空のまま Login ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>ブラウザの required バリデーションが発動してフォーム送信されない</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>ログイン</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>ページ直接アクセス（未認証）</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>未ログイン状態</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>ダッシュボード URL(/)に直接アクセス</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>ログインページが表示される</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>ログイン</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>ログアウト</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済み</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>サイドバー下部の Logout リンクをクリック</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>セッションが破棄されログインページへリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>■ ナビゲーション</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ナビゲーション</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>ページ切り替え</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>ログイン済み / Dashboardページ表示中</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>サイドバーの各メニュー（Console / Files / Logs / Backups / Status）を順にクリック</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>対応するページが表示され、アクティブなメニューがハイライトされる</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>ナビゲーション</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>ポーリングタイマー停止</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Console ページを表示してポーリング開始中</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>別ページ（Files など）に切り替え</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Console のポーリングタイマーが停止し、新しいページのタイマーが起動する</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ナビゲーション</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>モバイル：ハンバーガーメニュー表示</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>ブラウザ幅 700px 以下</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>ページを読み込む</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>上部に ☰ ボタンが表示され、サイドバーが非表示になる</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>ナビゲーション</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>モバイル：サイドバー開閉</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>ブラウザ幅 700px 以下</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>☰ ボタンをクリック → サイドバーが開く → オーバーレイをクリック</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>サイドバーが開き、オーバーレイクリックで閉じる</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ナビゲーション</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>モバイル：ページ遷移後にサイドバーが閉じる</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>ブラウザ幅 700px 以下 / サイドバーが開いた状態</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>サイドバーのメニュー項目をクリック</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>ページが切り替わると同時にサイドバーが自動で閉じる</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>■ 共通 UI</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>共通 UI</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>トースト通知（成功）</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>任意のページ</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>成功する操作（バックアップ作成など）を実行</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>右下に緑色のトースト通知が表示され、約3秒後に自動的に消える</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>共通 UI</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>トースト通知（エラー）</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>任意のページ</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>失敗する操作（空欄でバックアップなど）を実行</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>右下に赤色のトースト通知が表示され、約3秒後に自動的に消える</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>共通 UI</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>モーダル：OK / Cancel</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Files ページ / モーダルが開いた状態</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Cancel ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>モーダルが閉じ、操作は実行されない</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>共通 UI</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>モーダル：オーバーレイクリックで閉じる</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>モーダルが開いた状態</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>モーダル外側の暗いオーバーレイ部分をクリック</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>モーダルが閉じる</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>共通 UI</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>モーダル：自動フォーカス</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>入力フィールドを持つモーダルを開く</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>モーダルを表示させる（フォルダ作成・wget 等）</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>最初の入力フィールドに自動的にフォーカスが当たる</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>■ Dashboard</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>サーバー状態表示（Online）</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>サーバー起動中</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard ページを開く</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Server カードのドットが緑・テキストが 'Online' と表示される</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>サーバー状態表示（Offline）</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>サーバー停止中</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard ページを開く</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Server カードのドットが赤・テキストが 'Offline' と表示される</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Bot 状態表示</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Bot 起動中（常時）</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard ページを開く</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Bot カードのドットが常に緑・'Online' と表示される</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>IP 表示</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>allow.ip=true</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard ページを開く</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Server IP カードに外部 IP アドレスが表示される</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>IP 表示（無効）</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>allow.ip=false</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard ページを開く</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Server IP カードに 'N/A' が表示される</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>ライブログ自動更新</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>サーバー起動中</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard ページを表示したまま 5 秒以上待機</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>ライブログエリアが自動更新されサーバーログが追記される</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>ライブログ自動スクロール</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>ライブログが画面下端付近までスクロール済み</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>新しいログが追加される</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>ライブログが最下部まで自動スクロールする</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Start ボタン</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>サーバー停止中</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Start ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>成功トーストが表示され、ステータスが Online に変わる</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Start ボタン（すでに起動中）</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>サーバー起動中</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Start ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>「すでに起動中です」旨のエラートーストが表示される</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Stop ボタン</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>サーバー起動中</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Stop ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>成功トーストが表示され、ステータスが Offline に変わる</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Stop ボタン（すでに停止中）</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>サーバー停止中</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Stop ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>「すでに停止中です」旨のエラートーストが表示される</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>クイックバックアップ（正常）</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>サーバー停止中 / 対象フォルダが存在する</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>フォルダ名入力欄に 'world' を入力して Backup ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>成功トーストが表示される</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>クイックバックアップ（フォルダ名空欄）</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>フォルダ名入力欄を空にして Backup ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>'Enter folder name' エラートーストが表示される</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>クイックバックアップ（サーバー起動中）</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>サーバー起動中</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>フォルダ名を入力して Backup ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>「サーバーが起動中です」旨のエラートーストが表示される</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>■ Console</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>コンソール出力表示</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>サーバー起動中</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Console ページに遷移する</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>サーバーのコンソール出力が ANSI カラー付きで表示される</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>コンソール自動更新（5秒）</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Console ページ表示中</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>5 秒以上待機</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>コンソール出力が自動的に更新される</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>コンソール自動スクロール</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Console が最下部付近までスクロール済み</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>新しいログが追加される</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>コンソールが最下部まで自動スクロールする</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>コマンド送信（Enter キー）</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>サーバー起動中 / allow_mccmd に 'list' が設定済み</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>入力欄に 'list' と入力して Enter キーを押す</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>コマンドが送信されコンソールにサーバーの応答が表示される</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>コマンド送信（Send ボタン）</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>サーバー起動中</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>入力欄にコマンドを入力して Send ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>コマンドが送信され入力欄がクリアされる</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>空コマンドは送信しない</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>入力欄を空のまま Enter または Send ボタンを押す</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>API リクエストが送信されない（何も起きない）</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>コマンド履歴（↑キー）</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>過去にコマンドを送信済み</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>入力欄で ↑ キーを押す</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>直前に送信したコマンドが入力欄に表示される</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>コマンド履歴（↓キー）</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>↑ キーで履歴を遡った状態</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>↓ キーを押す</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>より新しいコマンドに戻り、最新まで進むと入力欄が空になる</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Console</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>コマンド送信（サーバー停止中）</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>サーバー停止中</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>入力欄にコマンドを入力して Send</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>'Server is not running' エラートーストが表示される</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>■ Files</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+      <c r="I45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>ファイル一覧表示</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>サーバールートにファイル・フォルダが存在する</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Files ページに遷移する</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>ファイル名・タイプ（dir/file）・サイズ・操作ボタンが一覧表示される</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>ディレクトリ移動（クリック）</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>ファイル一覧にディレクトリが存在する</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>ディレクトリ名（青字）をクリック</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>そのディレクトリ内に移動し、パンくずリストが更新される</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>パンくずナビゲーション</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>深い階層に移動済み</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>パンくずの任意の項目をクリック</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>クリックした階層に直接ジャンプする</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Up ボタン</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>サブディレクトリ内を表示中</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>↑ Up ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>1 階層上に移動してファイル一覧が更新される</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Server Root クリック</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>サブディレクトリ内を表示中</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>パンくずの 'Server Root' をクリック</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>サーバールートに移動してファイル一覧が更新される</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>ファイルダウンロード</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>ファイルが存在する</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>ファイル行の ↓ ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>ブラウザのダウンロードが開始される</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>ディレクトリダウンロード（ZIP）</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>ディレクトリが存在する</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>ディレクトリ行の ↓ ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>&lt;ディレクトリ名&gt;.zip としてダウンロードが開始される</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>.zip ファイルの Unzip ボタン表示</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>.zip ファイルが存在する</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Files ページにアクセス</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>.zip ファイルの行のみに '⎘ Unzip' ボタンが表示される</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Unzip 実行（正常）</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>有効な .zip ファイルが存在する</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>.zip ファイルの Unzip ボタン → Extract ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>ZIP が展開され成功トースト（'Extracted N files'）が表示されファイル一覧が更新される</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Unzip 実行（破損 zip）</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>破損した .zip ファイルが存在する</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>.zip ファイルの Unzip → Extract</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>エラートーストが表示される</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr"/>
+      <c r="I55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>ファイル名変更・移動（✎ ボタン）</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>ファイルが存在する</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>ファイル行の ✎ ボタン → 新パスを入力して OK</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>ファイルが移動/リネームされ成功トーストが表示されファイル一覧が更新される</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>ファイル名変更（パス変更なし）</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Rename モーダルが開いた状態</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>パスを変更せずに OK をクリック</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>何も変化しないまま（src === dst のため API 呼び出しなし）モーダルが閉じる</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>ファイル削除（✕ ボタン）</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>ファイルが存在する</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>ファイル行の ✕ ボタン → 確認ダイアログで Delete をクリック</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>ファイルが削除され成功トーストが表示されファイル一覧が更新される</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>ディレクトリ削除（🗑 ボタン）</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>ディレクトリが存在する</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>ディレクトリ行の 🗑 ボタン → 確認ダイアログで Delete</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>ディレクトリが再帰的に削除され成功トーストが表示されファイル一覧が更新される</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>削除確認ダイアログ・Cancel</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>削除確認ダイアログが表示中</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Cancel ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>ダイアログが閉じ、ファイル・ディレクトリは削除されない</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>フォルダ作成（＋ Folder）</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>任意のディレクトリを表示中</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>＋ Folder ボタン → フォルダ名入力 → OK</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>フォルダが作成され成功トーストが表示されファイル一覧が更新される</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr"/>
+      <c r="I61" s="4" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>フォルダ作成（名前空欄）</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>New Folder モーダルが開いた状態</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>フォルダ名欄を空のまま OK をクリック</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>'Enter folder name' エラートーストが表示される</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr"/>
+      <c r="I62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>ファイルアップロード（↑ Upload）</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>同名ファイルが存在しない</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>↑ Upload ボタン → ファイルを選択 → OK</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>ファイルがアップロードされ成功トーストが表示されファイル一覧が更新される</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr"/>
+      <c r="I63" s="4" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>ファイルアップロード（ファイル未選択）</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Upload モーダルが開いた状態</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>ファイルを選択せず OK をクリック</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>'Select a file' エラートーストが表示される</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr"/>
+      <c r="I64" s="5" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>ファイルアップロード（同名ファイル存在）</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>同名ファイルがすでに存在する</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>同名ファイルを選択して Upload → OK</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>'file already exists' エラートーストが表示される</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr"/>
+      <c r="I65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>wget でファイル取得（↓ wget）</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>有効な URL / 保存先が存在しない</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>↓ wget ボタン → URL 入力 → OK</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>'Downloading…' トースト後、成功トーストが表示されファイル一覧が更新される</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>wget（URL 空欄）</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>wget モーダルが開いた状態</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>URL 欄を空のまま OK をクリック</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>'Enter URL' エラートーストが表示される</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr"/>
+      <c r="I67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>wget（無効 URL / ネットワークエラー）</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>存在しない URL を指定</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>無効な URL を入力して OK</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>エラートーストが表示される</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr"/>
+      <c r="I68" s="5" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>空ディレクトリの表示</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>空のディレクトリに移動</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>空のディレクトリをクリックして移動</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>'Empty directory' と表示される</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr"/>
+      <c r="I69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t>■ Logs</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n"/>
+      <c r="C70" s="3" t="n"/>
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+      <c r="I70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Logs</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>ログファイル一覧読み込み</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>ログファイルが存在する</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Logs ページに遷移する</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>ドロップダウンにログファイル名が一覧表示される</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr"/>
+      <c r="I71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Logs</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>ログファイル一覧読み込み（ファイルなし）</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>ログファイルが存在しない</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Logs ページに遷移する</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>ドロップダウンには '— Select log file —' のみ表示される</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Logs</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>ログ内容表示</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>ドロップダウンにログファイルが存在する</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>ドロップダウンからログファイルを選択</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>ログの内容がテキストエリアに表示され、最下部に自動スクロールする</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr"/>
+      <c r="I73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Logs</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>ログ内容表示（空ファイル）</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>内容が空のログファイルを選択</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>空のログファイルを選択</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>テキストエリアに '(empty)' と表示される</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr"/>
+      <c r="I74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Logs</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>リスト更新ボタン（↺）</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Logs ページ表示中</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>↺ Refresh list ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>ログファイル一覧が再取得されドロップダウンが更新される</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr"/>
+      <c r="I75" s="4" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Logs</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>ログ内容取得エラー</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>API が失敗する状態（サーバーエラーなど）</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>ドロップダウンからファイルを選択</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>テキストエリアに 'Error: ...' と表示される</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr"/>
+      <c r="I76" s="5" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="16" t="inlineStr">
+        <is>
+          <t>■ Backups</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n"/>
+      <c r="C77" s="3" t="n"/>
+      <c r="D77" s="3" t="n"/>
+      <c r="E77" s="3" t="n"/>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+      <c r="I77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Backups</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>バックアップ一覧表示</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>バックアップが存在する</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>Backups ページに遷移する</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>バックアップ名が一覧で表示され、各行に Apply ボタンがある</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr"/>
+      <c r="I78" s="4" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Backups</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>バックアップ一覧表示（0件）</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>バックアップが存在しない</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Backups ページに遷移する</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>'No backups found' と表示される</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr"/>
+      <c r="I79" s="4" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Backups</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>一覧更新ボタン（↺）</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Backups ページ表示中</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>バックアップカードの ↺ ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>バックアップ一覧が再取得される</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr"/>
+      <c r="I80" s="4" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Backups</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>バックアップ作成（Run Backup）</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>サーバー停止中 / 対象フォルダが存在する</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>フォルダ名 'world' を入力して Run Backup ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>'Creating backup…' トースト後に成功トーストが表示され一覧が更新される</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr"/>
+      <c r="I81" s="4" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Backups</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>バックアップ作成（フォルダ名空欄）</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>フォルダ名欄を空にして Run Backup をクリック</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>'Enter folder name' エラートーストが表示される</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr"/>
+      <c r="I82" s="5" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Backups</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>バックアップ作成（サーバー起動中）</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>サーバー起動中</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>フォルダ名を入力して Run Backup をクリック</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>「サーバーが起動中です」旨のエラートーストが表示される</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr"/>
+      <c r="I83" s="5" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Backups</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>バックアップ作成（対象フォルダなし）</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>サーバー停止中 / 対象フォルダが存在しない</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>存在しないフォルダ名を入力して Run Backup</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>「データが見つかりません」旨のエラートーストが表示される</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr"/>
+      <c r="I84" s="5" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Backups</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>バックアップ適用（Apply）</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>バックアップが存在する / サーバー停止中</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>↩ Apply ボタン → 展開先パスを入力して Apply をクリック</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>'Applying backup…' トースト後に成功トーストが表示される</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr"/>
+      <c r="I85" s="4" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Backups</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>バックアップ適用（展開先空欄）</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>Apply モーダルが開いた状態</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>展開先欄を空にして Apply をクリック</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>'Enter destination path' エラートーストが表示されモーダルが閉じない</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr"/>
+      <c r="I86" s="5" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Backups</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>バックアップ適用（サーバー起動中）</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>エラー</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>サーバー起動中</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>↩ Apply → 展開先を入力して Apply</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>「サーバーが起動中です」旨のエラートーストが表示される</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr"/>
+      <c r="I87" s="5" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>Backups</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>バックアップ適用モーダル・Cancel</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Apply モーダルが開いた状態</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>Cancel ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>モーダルが閉じ、バックアップ適用は実行されない</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr"/>
+      <c r="I88" s="4" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>■ Status</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n"/>
+      <c r="C89" s="3" t="n"/>
+      <c r="D89" s="3" t="n"/>
+      <c r="E89" s="3" t="n"/>
+      <c r="F89" s="3" t="n"/>
+      <c r="G89" s="3" t="n"/>
+      <c r="H89" s="3" t="n"/>
+      <c r="I89" s="3" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>CPU 使用率表示</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>Status ページを開く</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>Status ページに遷移する</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>CPU 使用率（%）とプログレスバーが表示される</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr"/>
+      <c r="I90" s="4" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>CPU 80% 超でバー赤色</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>CPU 使用率が 80% を超えている状態</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>Status ページを開く</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>CPU バーが赤色（var(--red)）で表示される</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr"/>
+      <c r="I91" s="4" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>システムメモリ表示</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>Status ページに遷移する</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>システムメモリ使用率・使用量・合計量がバーとラベルで表示される</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr"/>
+      <c r="I92" s="4" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>メモリ 80% 超でバー赤色</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>システムメモリ使用率が 80% 超</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>Status ページを開く</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>システムメモリバーが赤色で表示される</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr"/>
+      <c r="I93" s="4" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Bot メモリ表示</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>Status ページに遷移する</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>Bot プロセスのメモリ使用量がバー付きで表示される</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr"/>
+      <c r="I94" s="4" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>サーバーメモリ表示（起動中）</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>サーバー起動中</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>Status ページに遷移する</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>サーバープロセスのメモリ使用量が表示される</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr"/>
+      <c r="I95" s="4" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>サーバーメモリ表示（停止中）</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>サーバー停止中</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>Status ページに遷移する</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>Server Memory カードに '—' が表示される</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr"/>
+      <c r="I96" s="4" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>接続状態（Online）</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>サーバー起動中</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>Status ページに遷移する</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>Connection カードの Server ドットが緑・'Server: Online' と表示される</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr"/>
+      <c r="I97" s="4" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>接続状態（Offline）</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>サーバー停止中</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>Status ページに遷移する</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>Connection カードの Server ドットが赤・'Server: Offline' と表示される</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr"/>
+      <c r="I98" s="4" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>↺ Refresh ボタン</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Status ページ表示中</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>↺ Refresh ボタンをクリック</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>ステータス情報が再取得されすべての値が更新される</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr"/>
+      <c r="I99" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A89:I89"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A20:I20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>